--- a/docs/safety/platform/safety-plan/LD-SPL-001_safety-plan.xlsx
+++ b/docs/safety/platform/safety-plan/LD-SPL-001_safety-plan.xlsx
@@ -892,7 +892,7 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Confirm or revise when the HARA is complete (milestone M04); recompute review independence.</t>
+          <t>Draft HARA LD-HARA-001 0.1 yields five ASIL D safety goals (SG-001 to SG-005), consistent with the target. Closes when the HARA passes its confirmation review.</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Maintainer decision on the proposal in platform/README.md</t>
+          <t>Envelope confirmed by the maintainer on 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Confirms or revises the provisional ASIL D target</t>
+          <t>Drafts 0.1 of LD-ITD-001 and LD-HARA-001 complete; awaiting review</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2523,7 @@
       <c r="G8" s="5" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Draft complete</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       <c r="G9" s="6" t="inlineStr"/>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Draft complete</t>
         </is>
       </c>
     </row>

--- a/docs/safety/platform/safety-plan/LD-SPL-001_safety-plan.xlsx
+++ b/docs/safety/platform/safety-plan/LD-SPL-001_safety-plan.xlsx
@@ -659,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -893,6 +893,48 @@
       <c r="H9" s="6" t="inlineStr">
         <is>
           <t>Draft HARA LD-HARA-001 0.1 yields five ASIL D safety goals (SG-001 to SG-005), consistent with the target. Closes when the HARA passes its confirmation review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>A05</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Claude Code (FSC)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>panda microcontroller fault detection is insufficient for ASIL D: a software watchdog on the main loop and interrupt-rate monitoring only record faults; no lockstep core or independent hardware watchdog; no evidence that a recorded fault leads to a no-output state (FSC gap G1).</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Lead (vacant)</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Assess the STM32H7's safety mechanisms; decide on an external watchdog with relay cut-off and/or a second monitoring MCU in the TSC. Blocks the D(D) + QM(D) decomposition.</t>
         </is>
       </c>
     </row>
@@ -1140,10 +1182,14 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>FSC draft 0.1 complete; SOTIF and TARA not started</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -2751,7 +2797,7 @@
       <c r="G14" s="5" t="inlineStr"/>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Draft complete</t>
         </is>
       </c>
     </row>

--- a/docs/safety/platform/safety-plan/LD-SPL-001_safety-plan.xlsx
+++ b/docs/safety/platform/safety-plan/LD-SPL-001_safety-plan.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Open (design proposed)</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>Assess the STM32H7's safety mechanisms; decide on an external watchdog with relay cut-off and/or a second monitoring MCU in the TSC. Blocks the D(D) + QM(D) decomposition.</t>
+          <t>TSC LD-TSC-001 proposes layered measures: L1 firmware (escalate recorded faults to a latched no-output state, independent watchdog with program-flow checks, ECC reporting, inverted copies of safety state, code CRC), L2 relay supervisor with a toggling drive in the harness box, and L3 a diverse monitoring MCU if the FMEDA cannot reach ASIL D metrics. Still blocks the D(D) + QM(D) decomposition until implemented and verified.</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Includes the doer/checker independence argument</t>
+          <t>TSC draft 0.1 complete (LD-TSC-001), including a first DFA of the doer/checker split; existing-software assessment not started</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2835,7 @@
       <c r="G15" s="6" t="inlineStr"/>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Draft complete</t>
         </is>
       </c>
     </row>
